--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2B7FB36-7C97-4791-B160-017DCC709D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86C05D8-F18B-41FA-8717-183631D917C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -52,6 +52,21 @@
   </si>
   <si>
     <t>VNET861385071455169</t>
+  </si>
+  <si>
+    <t>VNET861385070686442</t>
+  </si>
+  <si>
+    <t>VNET861385071516655</t>
+  </si>
+  <si>
+    <t>VNET861385070669141</t>
+  </si>
+  <si>
+    <t>VNET861385071534161</t>
+  </si>
+  <si>
+    <t>STT</t>
   </si>
 </sst>
 </file>
@@ -118,9 +133,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -129,9 +142,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -142,16 +153,14 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -162,19 +171,16 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,82 +495,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
         <v>46304</v>
       </c>
-      <c r="B3" s="3">
+      <c r="C3" s="3">
         <v>46307</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
         <v>46304</v>
       </c>
-      <c r="B4" s="3">
+      <c r="C4" s="3">
         <v>46307</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
         <v>46304</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
         <v>46307</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46308</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46308</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46308</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46308</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86C05D8-F18B-41FA-8717-183631D917C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F33390-1415-4D61-96AD-834A7EB45ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -570,6 +570,9 @@
       <c r="B5" s="3">
         <v>46304</v>
       </c>
+      <c r="C5" s="3">
+        <v>46308</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
@@ -584,6 +587,9 @@
       <c r="B6" s="3">
         <v>46307</v>
       </c>
+      <c r="C6" s="3">
+        <v>46308</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
@@ -598,6 +604,9 @@
       <c r="B7" s="3">
         <v>46308</v>
       </c>
+      <c r="C7" s="3">
+        <v>46308</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
@@ -610,6 +619,9 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C8" s="3">
         <v>46308</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -626,6 +638,9 @@
       <c r="B9" s="3">
         <v>46308</v>
       </c>
+      <c r="C9" s="3">
+        <v>46308</v>
+      </c>
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
@@ -638,6 +653,9 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
+        <v>46308</v>
+      </c>
+      <c r="C10" s="3">
         <v>46308</v>
       </c>
       <c r="D10" s="1" t="s">

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F33390-1415-4D61-96AD-834A7EB45ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1B460-30F7-4AF6-9B15-EC88FE5FF078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
+    <workbookView xWindow="5220" yWindow="1170" windowWidth="21600" windowHeight="11835" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -67,6 +67,21 @@
   </si>
   <si>
     <t>STT</t>
+  </si>
+  <si>
+    <t>Kèm ổ cứng 256GB, nhận từ Hương, thiết bị hàn M2 sẵn lắp ổ cứng vào kiểm tra</t>
+  </si>
+  <si>
+    <t>Kèm ổ cứng 256GB, nhận từ A. Bảo</t>
+  </si>
+  <si>
+    <t>VNET861385070647956</t>
+  </si>
+  <si>
+    <t>VNET861385071455094</t>
+  </si>
+  <si>
+    <t>VNET861385071476173</t>
   </si>
 </sst>
 </file>
@@ -495,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
@@ -665,6 +680,48 @@
         <v>6</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46309</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46309</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46309</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1B460-30F7-4AF6-9B15-EC88FE5FF078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C973E8-D455-410F-966F-C4284C5BB806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="1170" windowWidth="21600" windowHeight="11835" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -82,6 +82,33 @@
   </si>
   <si>
     <t>VNET861385071476173</t>
+  </si>
+  <si>
+    <t>VNET861385070606028</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo, hàng của kho VNET</t>
+  </si>
+  <si>
+    <t>VNET861385071455334</t>
+  </si>
+  <si>
+    <t>VNET861385071455516</t>
+  </si>
+  <si>
+    <t>Hương báo lại đưa Quân. LĐ</t>
+  </si>
+  <si>
+    <t>Đưa cho Quân LĐ</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo, thiết bị của SEA</t>
+  </si>
+  <si>
+    <t>VNET861385071456845</t>
+  </si>
+  <si>
+    <t>VNET861385071531530</t>
   </si>
 </sst>
 </file>
@@ -175,26 +202,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,217 +542,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="36" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="7">
         <v>46304</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>46307</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="7">
         <v>46304</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <v>46307</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="7">
         <v>46304</v>
       </c>
-      <c r="C5" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7">
         <v>46307</v>
       </c>
-      <c r="C6" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
-        <v>46308</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B7" s="7">
+        <v>46308</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
-        <v>46308</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B8" s="7">
+        <v>46308</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
-        <v>46308</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="B9" s="7">
+        <v>46308</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
-        <v>46308</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="7">
+        <v>46308</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46308</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="7">
         <v>46309</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="C11" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="F11" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="7">
         <v>46309</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="F12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="7">
         <v>46309</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B16" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B18" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C973E8-D455-410F-966F-C4284C5BB806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036CA2D2-A153-45D4-8B8E-7C5F0E569661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -99,16 +99,19 @@
     <t>Hương báo lại đưa Quân. LĐ</t>
   </si>
   <si>
-    <t>Đưa cho Quân LĐ</t>
-  </si>
-  <si>
-    <t>Nhận từ A. Bảo, thiết bị của SEA</t>
-  </si>
-  <si>
     <t>VNET861385071456845</t>
   </si>
   <si>
     <t>VNET861385071531530</t>
+  </si>
+  <si>
+    <t>Trả A. Bảo</t>
+  </si>
+  <si>
+    <t>Trả cho Tuấn Anh</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo, thiết bị của SEA, kèm ổ cứng 256GB</t>
   </si>
 </sst>
 </file>
@@ -770,7 +773,7 @@
         <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -795,40 +798,58 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="7">
+        <v>46310</v>
+      </c>
+      <c r="C16" s="7">
         <v>46310</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
+        <v>46310</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="B18" s="7">
+        <v>46310</v>
+      </c>
+      <c r="C18" s="7">
+        <v>46310</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B17" s="7">
-        <v>46310</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B18" s="7">
-        <v>46310</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036CA2D2-A153-45D4-8B8E-7C5F0E569661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8906D8F-4A8D-4D5C-9F7E-D46F01038FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Nhận từ A. Bảo, thiết bị của SEA, kèm ổ cứng 256GB</t>
+  </si>
+  <si>
+    <t>Trả cho Hương CSKH</t>
   </si>
 </sst>
 </file>
@@ -780,22 +783,34 @@
       <c r="B14" s="7">
         <v>46310</v>
       </c>
+      <c r="C14" s="7">
+        <v>46311</v>
+      </c>
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="7">
         <v>46310</v>
       </c>
+      <c r="C15" s="7">
+        <v>46311</v>
+      </c>
       <c r="D15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8906D8F-4A8D-4D5C-9F7E-D46F01038FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA6FD78-EC9F-4E7A-A124-44A712E58F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -115,6 +115,36 @@
   </si>
   <si>
     <t>Trả cho Hương CSKH</t>
+  </si>
+  <si>
+    <t>VNET861385071534187</t>
+  </si>
+  <si>
+    <t>VNET861385071457165</t>
+  </si>
+  <si>
+    <t>VNET861385071517976</t>
+  </si>
+  <si>
+    <t>VNET861385071531365</t>
+  </si>
+  <si>
+    <t>VNET861385071526878</t>
+  </si>
+  <si>
+    <t>VNET861385071455383</t>
+  </si>
+  <si>
+    <t>VNET861385071457157</t>
+  </si>
+  <si>
+    <t>VNET861385071531274</t>
+  </si>
+  <si>
+    <t>VNET861385071534682</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo kèm ổ cứng 256 GB</t>
   </si>
 </sst>
 </file>
@@ -548,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -780,6 +810,9 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
       <c r="B14" s="7">
         <v>46310</v>
       </c>
@@ -797,6 +830,9 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
       <c r="B15" s="7">
         <v>46310</v>
       </c>
@@ -814,6 +850,9 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
       <c r="B16" s="7">
         <v>46310</v>
       </c>
@@ -830,7 +869,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
       <c r="B17" s="7">
         <v>46310</v>
       </c>
@@ -847,7 +889,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
       <c r="B18" s="7">
         <v>46310</v>
       </c>
@@ -864,8 +909,131 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46312</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA6FD78-EC9F-4E7A-A124-44A712E58F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFA6C68-4C7E-426C-A082-45933D86C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Nhận từ A. Bảo kèm ổ cứng 256 GB</t>
+  </si>
+  <si>
+    <t>Trả cho A. Bảo</t>
   </si>
 </sst>
 </file>
@@ -958,11 +961,17 @@
       <c r="B22" s="7">
         <v>46312</v>
       </c>
+      <c r="C22" s="7">
+        <v>46312</v>
+      </c>
       <c r="D22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1028,11 +1037,17 @@
       <c r="B27" s="7">
         <v>46312</v>
       </c>
+      <c r="C27" s="7">
+        <v>46312</v>
+      </c>
       <c r="D27" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFA6C68-4C7E-426C-A082-45933D86C2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D30E9-F781-4ABB-81B2-DB5E60589BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>Trả cho A. Bảo</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo kèm ổ cứng 256 GB, cầu chì</t>
+  </si>
+  <si>
+    <t>Trả cho Hưng</t>
   </si>
 </sst>
 </file>
@@ -919,11 +925,17 @@
       <c r="B19" s="7">
         <v>46312</v>
       </c>
+      <c r="C19" s="7">
+        <v>46314</v>
+      </c>
       <c r="D19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -933,11 +945,17 @@
       <c r="B20" s="7">
         <v>46312</v>
       </c>
+      <c r="C20" s="7">
+        <v>46314</v>
+      </c>
       <c r="D20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -947,11 +965,17 @@
       <c r="B21" s="7">
         <v>46312</v>
       </c>
+      <c r="C21" s="7">
+        <v>46314</v>
+      </c>
       <c r="D21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -981,11 +1005,17 @@
       <c r="B23" s="7">
         <v>46312</v>
       </c>
+      <c r="C23" s="7">
+        <v>46314</v>
+      </c>
       <c r="D23" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -995,11 +1025,17 @@
       <c r="B24" s="7">
         <v>46312</v>
       </c>
+      <c r="C24" s="7">
+        <v>46314</v>
+      </c>
       <c r="D24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1009,11 +1045,17 @@
       <c r="B25" s="7">
         <v>46312</v>
       </c>
+      <c r="C25" s="7">
+        <v>46314</v>
+      </c>
       <c r="D25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1023,11 +1065,17 @@
       <c r="B26" s="7">
         <v>46312</v>
       </c>
+      <c r="C26" s="7">
+        <v>46314</v>
+      </c>
       <c r="D26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D30E9-F781-4ABB-81B2-DB5E60589BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4CAC68-DBF3-4DA1-82D4-19081CC88DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -154,6 +154,18 @@
   </si>
   <si>
     <t>Trả cho Hưng</t>
+  </si>
+  <si>
+    <t>VNET861385071448305</t>
+  </si>
+  <si>
+    <t>VNET861385071456852</t>
+  </si>
+  <si>
+    <t>VNET861385071531969</t>
+  </si>
+  <si>
+    <t>VNET861385071457546</t>
   </si>
 </sst>
 </file>
@@ -587,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -1098,6 +1110,62 @@
         <v>40</v>
       </c>
     </row>
+    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46315</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46315</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46315</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46315</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4CAC68-DBF3-4DA1-82D4-19081CC88DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109B855-4368-464F-9CCE-7C09343819B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="47">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -1159,11 +1159,17 @@
       <c r="B31" s="7">
         <v>46315</v>
       </c>
+      <c r="C31" s="7">
+        <v>46315</v>
+      </c>
       <c r="D31" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4109B855-4368-464F-9CCE-7C09343819B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F90BAB-AB34-4018-84DD-F42D4967A66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -166,6 +166,18 @@
   </si>
   <si>
     <t>VNET861385071457546</t>
+  </si>
+  <si>
+    <t>VNET861385071455573</t>
+  </si>
+  <si>
+    <t>VNET861385071531456</t>
+  </si>
+  <si>
+    <t>VNET861385070688109</t>
+  </si>
+  <si>
+    <t>Chập 12V đã thay diode ss34, Trả cho Tuấn Anh</t>
   </si>
 </sst>
 </file>
@@ -599,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -1117,11 +1129,17 @@
       <c r="B28" s="7">
         <v>46315</v>
       </c>
+      <c r="C28" s="7">
+        <v>46316</v>
+      </c>
       <c r="D28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1131,11 +1149,17 @@
       <c r="B29" s="7">
         <v>46315</v>
       </c>
+      <c r="C29" s="7">
+        <v>46316</v>
+      </c>
       <c r="D29" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1145,11 +1169,17 @@
       <c r="B30" s="7">
         <v>46315</v>
       </c>
+      <c r="C30" s="7">
+        <v>46316</v>
+      </c>
       <c r="D30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>39</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1170,6 +1200,66 @@
       </c>
       <c r="F31" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46316</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46316</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46316</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F90BAB-AB34-4018-84DD-F42D4967A66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4B5014-7525-4796-B98E-8B973CCD2C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -178,6 +178,42 @@
   </si>
   <si>
     <t>Chập 12V đã thay diode ss34, Trả cho Tuấn Anh</t>
+  </si>
+  <si>
+    <t>VNET861385071448719</t>
+  </si>
+  <si>
+    <t>VNET861385071449402</t>
+  </si>
+  <si>
+    <t>VNET860879084176102</t>
+  </si>
+  <si>
+    <t>VNET861385071527298</t>
+  </si>
+  <si>
+    <t>VNET861385071455490</t>
+  </si>
+  <si>
+    <t>VNET861385071457124</t>
+  </si>
+  <si>
+    <t>VNET861385071531753</t>
+  </si>
+  <si>
+    <t>VNET861385071455839</t>
+  </si>
+  <si>
+    <t>VNET861385071486693</t>
+  </si>
+  <si>
+    <t>VNET861385071448461</t>
+  </si>
+  <si>
+    <t>VNET861385071535002</t>
+  </si>
+  <si>
+    <t>Thiết bị của kho VNET</t>
   </si>
 </sst>
 </file>
@@ -611,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -1262,6 +1298,160 @@
         <v>27</v>
       </c>
     </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46317</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4B5014-7525-4796-B98E-8B973CCD2C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F74127-65A0-49C0-827B-53038DC7D6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>Thiết bị của kho VNET</t>
+  </si>
+  <si>
+    <t>Thiết bị lô 1000 không hỗ trợ ổ cứng, ngược GX12 - 4P CAM1</t>
+  </si>
+  <si>
+    <t>Hương CSKH xuất kho, trả cho A. Bảo</t>
   </si>
 </sst>
 </file>
@@ -1305,11 +1311,17 @@
       <c r="B35" s="7">
         <v>46317</v>
       </c>
+      <c r="C35" s="7">
+        <v>46319</v>
+      </c>
       <c r="D35" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1319,14 +1331,20 @@
       <c r="B36" s="7">
         <v>46317</v>
       </c>
+      <c r="C36" s="7">
+        <v>46319</v>
+      </c>
       <c r="D36" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1338,6 +1356,9 @@
       </c>
       <c r="E37" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1347,11 +1368,17 @@
       <c r="B38" s="7">
         <v>46317</v>
       </c>
+      <c r="C38" s="7">
+        <v>46319</v>
+      </c>
       <c r="D38" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1417,11 +1444,17 @@
       <c r="B43" s="7">
         <v>46317</v>
       </c>
+      <c r="C43" s="7">
+        <v>46319</v>
+      </c>
       <c r="D43" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1431,11 +1464,17 @@
       <c r="B44" s="7">
         <v>46317</v>
       </c>
+      <c r="C44" s="7">
+        <v>46319</v>
+      </c>
       <c r="D44" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1445,11 +1484,17 @@
       <c r="B45" s="7">
         <v>46317</v>
       </c>
+      <c r="C45" s="7">
+        <v>46319</v>
+      </c>
       <c r="D45" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F74127-65A0-49C0-827B-53038DC7D6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C708B27-06B0-4921-9A26-5A189ECFFD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -1388,11 +1388,17 @@
       <c r="B39" s="7">
         <v>46317</v>
       </c>
+      <c r="C39" s="7">
+        <v>46320</v>
+      </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,11 +1408,17 @@
       <c r="B40" s="7">
         <v>46317</v>
       </c>
+      <c r="C40" s="7">
+        <v>46320</v>
+      </c>
       <c r="D40" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1416,11 +1428,17 @@
       <c r="B41" s="7">
         <v>46317</v>
       </c>
+      <c r="C41" s="7">
+        <v>46320</v>
+      </c>
       <c r="D41" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1430,11 +1448,17 @@
       <c r="B42" s="7">
         <v>46317</v>
       </c>
+      <c r="C42" s="7">
+        <v>46320</v>
+      </c>
       <c r="D42" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C708B27-06B0-4921-9A26-5A189ECFFD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF2BE3B-CD15-454A-AA92-82956F135688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="79">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -216,10 +216,52 @@
     <t>Thiết bị của kho VNET</t>
   </si>
   <si>
-    <t>Thiết bị lô 1000 không hỗ trợ ổ cứng, ngược GX12 - 4P CAM1</t>
-  </si>
-  <si>
     <t>Hương CSKH xuất kho, trả cho A. Bảo</t>
+  </si>
+  <si>
+    <t>26/010/2026</t>
+  </si>
+  <si>
+    <t>Thiết bị lô 1000 không hỗ trợ ổ cứng, ngược GX12 - 4P CAM1, trả lại kho VNET</t>
+  </si>
+  <si>
+    <t>Nhận từ A. Bảo</t>
+  </si>
+  <si>
+    <t>VNET861385071449428</t>
+  </si>
+  <si>
+    <t>VNET861385071448438</t>
+  </si>
+  <si>
+    <t>VNET861385071517695</t>
+  </si>
+  <si>
+    <t>VNET861385071517174</t>
+  </si>
+  <si>
+    <t>VNET861385071455722</t>
+  </si>
+  <si>
+    <t>VNET861385070647089</t>
+  </si>
+  <si>
+    <t>VNET861385071516671</t>
+  </si>
+  <si>
+    <t>VNET861385071531522</t>
+  </si>
+  <si>
+    <t>VNET861385071461431</t>
+  </si>
+  <si>
+    <t>VNET861385070692861</t>
+  </si>
+  <si>
+    <t>VNET861385071516523</t>
+  </si>
+  <si>
+    <t>Trả A. Bảo lấy ổ cứng từ thiết bị BH ID: VNET861385071517976</t>
   </si>
 </sst>
 </file>
@@ -653,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="2" customWidth="1"/>
@@ -1321,7 +1363,7 @@
         <v>62</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,16 +1383,19 @@
         <v>62</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="7">
         <v>46317</v>
       </c>
+      <c r="C37" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D37" s="2" t="s">
         <v>53</v>
       </c>
@@ -1358,7 +1403,7 @@
         <v>62</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,7 +1423,7 @@
         <v>62</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1398,7 +1443,7 @@
         <v>62</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,7 +1463,7 @@
         <v>62</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,7 +1483,7 @@
         <v>62</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,7 +1503,7 @@
         <v>62</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,7 +1523,7 @@
         <v>62</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,7 +1543,7 @@
         <v>62</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,7 +1563,232 @@
         <v>62</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" s="7">
+        <v>46321</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46321</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="7">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" s="7">
+        <v>46321</v>
       </c>
     </row>
   </sheetData>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF2BE3B-CD15-454A-AA92-82956F135688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2126ED3-DA1E-4B3C-8125-7B44B1B1C699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901113F3-2046-462A-9B8E-DD1C871034F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A093CA7-1040-4F68-8C07-3CE80224EFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -286,6 +286,21 @@
   </si>
   <si>
     <t>Ghi chú 2</t>
+  </si>
+  <si>
+    <t>Nhận từ kho VNET, Hương báo xuất cho KL</t>
+  </si>
+  <si>
+    <t>VNET861385071448354</t>
+  </si>
+  <si>
+    <t>VNET861385071460193</t>
+  </si>
+  <si>
+    <t>VNET861385071487345</t>
+  </si>
+  <si>
+    <t>VNET861385071531944</t>
   </si>
 </sst>
 </file>
@@ -732,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4737F8-152C-4E90-A6D8-6DCC789AEDB6}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
@@ -1967,6 +1982,62 @@
         <v>25</v>
       </c>
     </row>
+    <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46325</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46325</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46325</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46325</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
+++ b/5. Other/VNSH03 hàn thêm M2 NVMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A093CA7-1040-4F68-8C07-3CE80224EFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217D6EE7-FF5A-4822-9C23-A7E8E7FB6072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{EC3BDDC8-0DA6-465B-868D-CE194108D9E1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="93">
   <si>
     <t>200 Thiết bị VNSH03 hàn thêm khe M2</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>VNET861385071531944</t>
+  </si>
+  <si>
+    <t>Trả cho A. Lực</t>
   </si>
 </sst>
 </file>
@@ -1989,53 +1992,77 @@
       <c r="B64" s="2">
         <v>46325</v>
       </c>
+      <c r="C64" s="2">
+        <v>46326</v>
+      </c>
       <c r="D64" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="F64" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65" s="2">
         <v>46325</v>
       </c>
+      <c r="C65" s="2">
+        <v>46326</v>
+      </c>
       <c r="D65" s="1" t="s">
         <v>89</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="F65" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66" s="2">
         <v>46325</v>
       </c>
+      <c r="C66" s="2">
+        <v>46326</v>
+      </c>
       <c r="D66" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="F66" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67" s="2">
         <v>46325</v>
       </c>
+      <c r="C67" s="2">
+        <v>46326</v>
+      </c>
       <c r="D67" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>87</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
